--- a/data/performance/daily/signal_list_2026-07-06.xlsx
+++ b/data/performance/daily/signal_list_2026-07-06.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-07-06.xlsx
+++ b/data/performance/daily/signal_list_2026-07-06.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -563,12 +569,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,17 +611,22 @@
       <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -642,17 +658,22 @@
       <c r="G7" s="4" t="n">
         <v>-15</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -684,17 +705,22 @@
       <c r="G8" s="4" t="n">
         <v>-0.82</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -773,12 +804,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -815,12 +851,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -857,12 +898,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -894,17 +940,22 @@
       <c r="G13" s="4" t="n">
         <v>-0.83</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -941,12 +992,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -963,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -973,9 +1029,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1005,7 +1062,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1030,15 +1087,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1070,17 +1132,22 @@
       <c r="G5" s="4" t="n">
         <v>-5.13</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,12 +1184,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1159,12 +1231,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1196,17 +1273,22 @@
       <c r="G8" s="4" t="n">
         <v>-0.95</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1238,17 +1320,22 @@
       <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1280,17 +1367,22 @@
       <c r="G10" s="4" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1327,12 +1419,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1364,17 +1461,22 @@
       <c r="G12" s="4" t="n">
         <v>-15</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1411,12 +1513,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1448,17 +1555,22 @@
       <c r="G14" s="4" t="n">
         <v>-0.82</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1490,17 +1602,22 @@
       <c r="G15" s="4" t="n">
         <v>-1.22</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1537,12 +1654,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1574,17 +1696,22 @@
       <c r="G17" s="4" t="n">
         <v>-6.82</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1616,17 +1743,22 @@
       <c r="G18" s="4" t="n">
         <v>-2.64</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1663,12 +1795,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1705,12 +1842,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1747,12 +1889,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1789,12 +1936,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1831,12 +1983,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1873,12 +2030,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1910,17 +2072,22 @@
       <c r="G25" s="4" t="n">
         <v>-1.22</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1957,12 +2124,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1999,12 +2171,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2036,17 +2213,22 @@
       <c r="G28" s="4" t="n">
         <v>-2.94</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2078,17 +2260,22 @@
       <c r="G29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2120,17 +2307,22 @@
       <c r="G30" s="4" t="n">
         <v>-2.21</v>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2167,12 +2359,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2209,12 +2406,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2251,12 +2453,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2288,17 +2495,22 @@
       <c r="G34" s="4" t="n">
         <v>-1.08</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2335,12 +2547,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2372,17 +2589,22 @@
       <c r="G36" s="4" t="n">
         <v>-2.5</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2419,12 +2641,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2461,12 +2688,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2503,12 +2735,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2540,17 +2777,22 @@
       <c r="G40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2582,17 +2824,22 @@
       <c r="G41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2624,17 +2871,22 @@
       <c r="G42" s="4" t="n">
         <v>-0.51</v>
       </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2666,17 +2918,22 @@
       <c r="G43" s="4" t="n">
         <v>-0.71</v>
       </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2708,17 +2965,22 @@
       <c r="G44" s="4" t="n">
         <v>-5.19</v>
       </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2750,17 +3012,22 @@
       <c r="G45" s="4" t="n">
         <v>-2.04</v>
       </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2797,12 +3064,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2839,12 +3111,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2876,17 +3153,22 @@
       <c r="G48" s="4" t="n">
         <v>-0.63</v>
       </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2923,12 +3205,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2965,12 +3252,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-07-06.xlsx
+++ b/data/performance/daily/signal_list_2026-07-06.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>322</v>
       </c>
       <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
         <v>324</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>326</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>1.24</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>138</v>
       </c>
       <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
         <v>138</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>139</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>3400</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>2890</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>3640</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>7.06</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-15</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>610</v>
       </c>
       <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
         <v>605</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>615</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.82</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>1515</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>1515</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>1525</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>960</v>
       </c>
       <c r="D10" t="n">
-        <v>975</v>
+        <v/>
       </c>
       <c r="E10" t="n">
         <v>975</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>1.56</v>
+      <c r="F10" t="n">
+        <v>975</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H10" s="4" t="n">
+        <v>1.56</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>8600</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>8625</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>8700</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>0.29</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>404</v>
       </c>
       <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
         <v>450</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>454</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>12.38</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>11.39</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>1210</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>1200</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>1215</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-0.83</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -976,33 +1009,36 @@
         <v>585</v>
       </c>
       <c r="D14" t="n">
-        <v>595</v>
+        <v/>
       </c>
       <c r="E14" t="n">
         <v>595</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>1.71</v>
+      <c r="F14" t="n">
+        <v>595</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>1.71</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H14" s="4" t="n">
+        <v>1.71</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1019,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1027,12 +1063,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,45 +1099,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1121,33 +1163,36 @@
         <v>2730</v>
       </c>
       <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
         <v>2590</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>2930</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>7.33</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-5.13</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1168,33 +1213,36 @@
         <v>378</v>
       </c>
       <c r="D6" t="n">
-        <v>414</v>
+        <v/>
       </c>
       <c r="E6" t="n">
         <v>414</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>9.52</v>
+      <c r="F6" t="n">
+        <v>414</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>9.52</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H6" s="4" t="n">
+        <v>9.52</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1215,33 +1263,36 @@
         <v>3970</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>3690</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>3970</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-7.05</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1262,33 +1313,36 @@
         <v>105</v>
       </c>
       <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
         <v>104</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>108</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>2.86</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.95</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1309,33 +1363,36 @@
         <v>286</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>286</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>296</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>3.5</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,33 +1413,36 @@
         <v>153</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>138</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>160</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,33 +1463,36 @@
         <v>258</v>
       </c>
       <c r="D11" t="n">
-        <v>268</v>
+        <v/>
       </c>
       <c r="E11" t="n">
         <v>268</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>3.88</v>
+      <c r="F11" t="n">
+        <v>268</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>3.88</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H11" s="4" t="n">
+        <v>3.88</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1450,33 +1513,36 @@
         <v>3400</v>
       </c>
       <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
         <v>2890</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>3640</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>7.06</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-15</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1497,33 +1563,36 @@
         <v>1985</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>1885</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>1975</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-5.04</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1544,33 +1613,36 @@
         <v>610</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>605</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>615</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-0.82</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1591,33 +1663,36 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
         <v>81</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>83</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>1.22</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-1.22</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1638,33 +1713,36 @@
         <v>89</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>91</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>96</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>7.87</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>2.25</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1685,33 +1763,36 @@
         <v>132</v>
       </c>
       <c r="D17" t="n">
+        <v/>
+      </c>
+      <c r="E17" t="n">
         <v>123</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>147</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>11.36</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-6.82</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1732,33 +1813,36 @@
         <v>454</v>
       </c>
       <c r="D18" t="n">
+        <v/>
+      </c>
+      <c r="E18" t="n">
         <v>442</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>458</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-2.64</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1779,33 +1863,36 @@
         <v>24000</v>
       </c>
       <c r="D19" t="n">
+        <v/>
+      </c>
+      <c r="E19" t="n">
         <v>23800</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>24000</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-0.83</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1826,33 +1913,36 @@
         <v>830</v>
       </c>
       <c r="D20" t="n">
+        <v/>
+      </c>
+      <c r="E20" t="n">
         <v>835</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>850</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>2.41</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1873,33 +1963,36 @@
         <v>9000</v>
       </c>
       <c r="D21" t="n">
-        <v>9500</v>
+        <v/>
       </c>
       <c r="E21" t="n">
         <v>9500</v>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>5.56</v>
+      <c r="F21" t="n">
+        <v>9500</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>5.56</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H21" s="4" t="n">
+        <v>5.56</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1920,33 +2013,36 @@
         <v>760</v>
       </c>
       <c r="D22" t="n">
-        <v>835</v>
+        <v/>
       </c>
       <c r="E22" t="n">
         <v>835</v>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>9.869999999999999</v>
+      <c r="F22" t="n">
+        <v>835</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H22" s="4" t="n">
+        <v>9.869999999999999</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1967,33 +2063,36 @@
         <v>204</v>
       </c>
       <c r="D23" t="n">
+        <v/>
+      </c>
+      <c r="E23" t="n">
         <v>210</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>240</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>17.65</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>2.94</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2014,33 +2113,36 @@
         <v>290</v>
       </c>
       <c r="D24" t="n">
+        <v/>
+      </c>
+      <c r="E24" t="n">
         <v>328</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>342</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>17.93</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>13.1</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2061,33 +2163,36 @@
         <v>82</v>
       </c>
       <c r="D25" t="n">
+        <v/>
+      </c>
+      <c r="E25" t="n">
         <v>81</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>85</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>3.66</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>-1.22</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2108,33 +2213,36 @@
         <v>191</v>
       </c>
       <c r="D26" t="n">
-        <v>210</v>
+        <v/>
       </c>
       <c r="E26" t="n">
         <v>210</v>
       </c>
-      <c r="F26" s="4" t="n">
-        <v>9.949999999999999</v>
+      <c r="F26" t="n">
+        <v>210</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H26" s="4" t="n">
+        <v>9.949999999999999</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2155,33 +2263,36 @@
         <v>194</v>
       </c>
       <c r="D27" t="n">
-        <v>212</v>
+        <v/>
       </c>
       <c r="E27" t="n">
         <v>212</v>
       </c>
-      <c r="F27" s="4" t="n">
-        <v>9.279999999999999</v>
+      <c r="F27" t="n">
+        <v>212</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H27" s="4" t="n">
+        <v>9.279999999999999</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2202,33 +2313,36 @@
         <v>408</v>
       </c>
       <c r="D28" t="n">
+        <v/>
+      </c>
+      <c r="E28" t="n">
         <v>396</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>410</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>0.49</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>-2.94</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2249,33 +2363,36 @@
         <v>68</v>
       </c>
       <c r="D29" t="n">
+        <v/>
+      </c>
+      <c r="E29" t="n">
         <v>68</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>69</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>1.47</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2296,33 +2413,36 @@
         <v>136</v>
       </c>
       <c r="D30" t="n">
+        <v/>
+      </c>
+      <c r="E30" t="n">
         <v>133</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>138</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>1.47</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>-2.21</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2343,33 +2463,36 @@
         <v>8600</v>
       </c>
       <c r="D31" t="n">
+        <v/>
+      </c>
+      <c r="E31" t="n">
         <v>8625</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>8700</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>0.29</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2390,33 +2513,36 @@
         <v>137</v>
       </c>
       <c r="D32" t="n">
-        <v>147</v>
+        <v/>
       </c>
       <c r="E32" t="n">
         <v>147</v>
       </c>
-      <c r="F32" s="4" t="n">
-        <v>7.3</v>
+      <c r="F32" t="n">
+        <v>147</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>7.3</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H32" s="4" t="n">
+        <v>7.3</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2437,33 +2563,36 @@
         <v>404</v>
       </c>
       <c r="D33" t="n">
+        <v/>
+      </c>
+      <c r="E33" t="n">
         <v>450</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>454</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>12.38</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>11.39</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2484,33 +2613,36 @@
         <v>93</v>
       </c>
       <c r="D34" t="n">
+        <v/>
+      </c>
+      <c r="E34" t="n">
         <v>92</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>100</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>7.53</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>-1.08</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2531,33 +2663,36 @@
         <v>1330</v>
       </c>
       <c r="D35" t="n">
+        <v/>
+      </c>
+      <c r="E35" t="n">
         <v>1340</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>1380</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>3.76</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2578,33 +2713,36 @@
         <v>800</v>
       </c>
       <c r="D36" t="n">
+        <v/>
+      </c>
+      <c r="E36" t="n">
         <v>780</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>825</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>3.12</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>-2.5</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2625,33 +2763,36 @@
         <v>700</v>
       </c>
       <c r="D37" t="n">
+        <v/>
+      </c>
+      <c r="E37" t="n">
         <v>715</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>725</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>3.57</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>2.14</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2672,33 +2813,36 @@
         <v>220</v>
       </c>
       <c r="D38" t="n">
+        <v/>
+      </c>
+      <c r="E38" t="n">
         <v>232</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>240</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>9.09</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>5.45</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2719,33 +2863,36 @@
         <v>145</v>
       </c>
       <c r="D39" t="n">
+        <v/>
+      </c>
+      <c r="E39" t="n">
         <v>143</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>145</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>-1.38</v>
       </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="J39" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2766,33 +2913,36 @@
         <v>620</v>
       </c>
       <c r="D40" t="n">
+        <v/>
+      </c>
+      <c r="E40" t="n">
         <v>620</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>635</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>2.42</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2813,33 +2963,36 @@
         <v>308</v>
       </c>
       <c r="D41" t="n">
+        <v/>
+      </c>
+      <c r="E41" t="n">
         <v>308</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>324</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>5.19</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2860,33 +3013,36 @@
         <v>390</v>
       </c>
       <c r="D42" t="n">
+        <v/>
+      </c>
+      <c r="E42" t="n">
         <v>388</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>436</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>11.79</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>-0.51</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2907,33 +3063,36 @@
         <v>282</v>
       </c>
       <c r="D43" t="n">
+        <v/>
+      </c>
+      <c r="E43" t="n">
         <v>280</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>284</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>-0.71</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2954,33 +3113,36 @@
         <v>135</v>
       </c>
       <c r="D44" t="n">
+        <v/>
+      </c>
+      <c r="E44" t="n">
         <v>128</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>144</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>6.67</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>-5.19</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3001,33 +3163,36 @@
         <v>98</v>
       </c>
       <c r="D45" t="n">
+        <v/>
+      </c>
+      <c r="E45" t="n">
         <v>96</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>102</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>4.08</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>-2.04</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3048,33 +3213,36 @@
         <v>585</v>
       </c>
       <c r="D46" t="n">
-        <v>595</v>
+        <v/>
       </c>
       <c r="E46" t="n">
         <v>595</v>
       </c>
-      <c r="F46" s="4" t="n">
-        <v>1.71</v>
+      <c r="F46" t="n">
+        <v>595</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>1.71</v>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H46" s="4" t="n">
+        <v>1.71</v>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3095,33 +3263,36 @@
         <v>5325</v>
       </c>
       <c r="D47" t="n">
+        <v/>
+      </c>
+      <c r="E47" t="n">
         <v>5500</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>5525</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>3.76</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>3.29</v>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3142,33 +3313,36 @@
         <v>159</v>
       </c>
       <c r="D48" t="n">
+        <v/>
+      </c>
+      <c r="E48" t="n">
         <v>158</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>165</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="G48" s="4" t="n">
         <v>3.77</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>-0.63</v>
       </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3189,33 +3363,36 @@
         <v>414</v>
       </c>
       <c r="D49" t="n">
+        <v/>
+      </c>
+      <c r="E49" t="n">
         <v>488</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>515</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>24.4</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>17.87</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3236,33 +3413,36 @@
         <v>189775</v>
       </c>
       <c r="D50" t="n">
+        <v/>
+      </c>
+      <c r="E50" t="n">
         <v>198950</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>199000</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>4.86</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>4.83</v>
       </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-07-06.xlsx
+++ b/data/performance/daily/signal_list_2026-07-06.xlsx
@@ -559,7 +559,7 @@
         <v>322</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>322</v>
       </c>
       <c r="E5" t="n">
         <v>324</v>
@@ -609,7 +609,7 @@
         <v>138</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>139</v>
       </c>
       <c r="E6" t="n">
         <v>138</v>
@@ -659,7 +659,7 @@
         <v>3400</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>3600</v>
       </c>
       <c r="E7" t="n">
         <v>2890</v>
@@ -709,7 +709,7 @@
         <v>610</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>610</v>
       </c>
       <c r="E8" t="n">
         <v>605</v>
@@ -759,7 +759,7 @@
         <v>1515</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>1515</v>
       </c>
       <c r="E9" t="n">
         <v>1515</v>
@@ -809,7 +809,7 @@
         <v>960</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>965</v>
       </c>
       <c r="E10" t="n">
         <v>975</v>
@@ -859,7 +859,7 @@
         <v>8600</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>8700</v>
       </c>
       <c r="E11" t="n">
         <v>8625</v>
@@ -909,7 +909,7 @@
         <v>404</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>406</v>
       </c>
       <c r="E12" t="n">
         <v>450</v>
@@ -959,7 +959,7 @@
         <v>1210</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>1210</v>
       </c>
       <c r="E13" t="n">
         <v>1200</v>
@@ -1009,7 +1009,7 @@
         <v>585</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>585</v>
       </c>
       <c r="E14" t="n">
         <v>595</v>
@@ -1163,7 +1163,7 @@
         <v>2730</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>2760</v>
       </c>
       <c r="E5" t="n">
         <v>2590</v>
@@ -1213,7 +1213,7 @@
         <v>378</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>404</v>
       </c>
       <c r="E6" t="n">
         <v>414</v>
@@ -1263,7 +1263,7 @@
         <v>3970</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>3970</v>
       </c>
       <c r="E7" t="n">
         <v>3690</v>
@@ -1313,7 +1313,7 @@
         <v>105</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>91.06</v>
       </c>
       <c r="E8" t="n">
         <v>104</v>
@@ -1363,7 +1363,7 @@
         <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>296</v>
       </c>
       <c r="E9" t="n">
         <v>286</v>
@@ -1413,7 +1413,7 @@
         <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>156</v>
       </c>
       <c r="E10" t="n">
         <v>138</v>
@@ -1463,7 +1463,7 @@
         <v>258</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>262</v>
       </c>
       <c r="E11" t="n">
         <v>268</v>
@@ -1513,7 +1513,7 @@
         <v>3400</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>3600</v>
       </c>
       <c r="E12" t="n">
         <v>2890</v>
@@ -1563,7 +1563,7 @@
         <v>1985</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>1970</v>
       </c>
       <c r="E13" t="n">
         <v>1885</v>
@@ -1613,7 +1613,7 @@
         <v>610</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>610</v>
       </c>
       <c r="E14" t="n">
         <v>605</v>
@@ -1663,7 +1663,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>82</v>
       </c>
       <c r="E15" t="n">
         <v>81</v>
@@ -1713,7 +1713,7 @@
         <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>86.31</v>
       </c>
       <c r="E16" t="n">
         <v>91</v>
@@ -1763,7 +1763,7 @@
         <v>132</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>133.46</v>
       </c>
       <c r="E17" t="n">
         <v>123</v>
@@ -1813,7 +1813,7 @@
         <v>454</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>456</v>
       </c>
       <c r="E18" t="n">
         <v>442</v>
@@ -1863,7 +1863,7 @@
         <v>24000</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>24000</v>
       </c>
       <c r="E19" t="n">
         <v>23800</v>
@@ -1913,7 +1913,7 @@
         <v>830</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>775</v>
       </c>
       <c r="E20" t="n">
         <v>835</v>
@@ -1963,7 +1963,7 @@
         <v>9000</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>9000</v>
       </c>
       <c r="E21" t="n">
         <v>9500</v>
@@ -2013,7 +2013,7 @@
         <v>760</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>815</v>
       </c>
       <c r="E22" t="n">
         <v>835</v>
@@ -2063,7 +2063,7 @@
         <v>204</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>210</v>
       </c>
       <c r="E23" t="n">
         <v>210</v>
@@ -2113,7 +2113,7 @@
         <v>290</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>179.01</v>
       </c>
       <c r="E24" t="n">
         <v>328</v>
@@ -2163,7 +2163,7 @@
         <v>82</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>85</v>
       </c>
       <c r="E25" t="n">
         <v>81</v>
@@ -2213,7 +2213,7 @@
         <v>191</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>193</v>
       </c>
       <c r="E26" t="n">
         <v>210</v>
@@ -2263,7 +2263,7 @@
         <v>194</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>194</v>
       </c>
       <c r="E27" t="n">
         <v>212</v>
@@ -2313,7 +2313,7 @@
         <v>408</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>410</v>
       </c>
       <c r="E28" t="n">
         <v>396</v>
@@ -2363,7 +2363,7 @@
         <v>68</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>69</v>
       </c>
       <c r="E29" t="n">
         <v>68</v>
@@ -2413,7 +2413,7 @@
         <v>136</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>136</v>
       </c>
       <c r="E30" t="n">
         <v>133</v>
@@ -2463,7 +2463,7 @@
         <v>8600</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>8700</v>
       </c>
       <c r="E31" t="n">
         <v>8625</v>
@@ -2513,7 +2513,7 @@
         <v>137</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>137</v>
       </c>
       <c r="E32" t="n">
         <v>147</v>
@@ -2563,7 +2563,7 @@
         <v>404</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>406</v>
       </c>
       <c r="E33" t="n">
         <v>450</v>
@@ -2613,7 +2613,7 @@
         <v>93</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>93</v>
       </c>
       <c r="E34" t="n">
         <v>92</v>
@@ -2663,7 +2663,7 @@
         <v>1330</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>1120.43</v>
       </c>
       <c r="E35" t="n">
         <v>1340</v>
@@ -2713,7 +2713,7 @@
         <v>800</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>760</v>
       </c>
       <c r="E36" t="n">
         <v>780</v>
@@ -2763,7 +2763,7 @@
         <v>700</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>700</v>
       </c>
       <c r="E37" t="n">
         <v>715</v>
@@ -2813,7 +2813,7 @@
         <v>220</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>224</v>
       </c>
       <c r="E38" t="n">
         <v>232</v>
@@ -2863,7 +2863,7 @@
         <v>145</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>145</v>
       </c>
       <c r="E39" t="n">
         <v>143</v>
@@ -2913,7 +2913,7 @@
         <v>620</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>625</v>
       </c>
       <c r="E40" t="n">
         <v>620</v>
@@ -2963,7 +2963,7 @@
         <v>308</v>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>308</v>
       </c>
       <c r="E41" t="n">
         <v>308</v>
@@ -3013,7 +3013,7 @@
         <v>390</v>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>390</v>
       </c>
       <c r="E42" t="n">
         <v>388</v>
@@ -3063,7 +3063,7 @@
         <v>282</v>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>284</v>
       </c>
       <c r="E43" t="n">
         <v>280</v>
@@ -3113,7 +3113,7 @@
         <v>135</v>
       </c>
       <c r="D44" t="n">
-        <v/>
+        <v>139</v>
       </c>
       <c r="E44" t="n">
         <v>128</v>
@@ -3163,7 +3163,7 @@
         <v>98</v>
       </c>
       <c r="D45" t="n">
-        <v/>
+        <v>99</v>
       </c>
       <c r="E45" t="n">
         <v>96</v>
@@ -3213,7 +3213,7 @@
         <v>585</v>
       </c>
       <c r="D46" t="n">
-        <v/>
+        <v>585</v>
       </c>
       <c r="E46" t="n">
         <v>595</v>
@@ -3263,7 +3263,7 @@
         <v>5325</v>
       </c>
       <c r="D47" t="n">
-        <v/>
+        <v>5400</v>
       </c>
       <c r="E47" t="n">
         <v>5500</v>
@@ -3313,7 +3313,7 @@
         <v>159</v>
       </c>
       <c r="D48" t="n">
-        <v/>
+        <v>160</v>
       </c>
       <c r="E48" t="n">
         <v>158</v>
@@ -3363,7 +3363,7 @@
         <v>414</v>
       </c>
       <c r="D49" t="n">
-        <v/>
+        <v>416</v>
       </c>
       <c r="E49" t="n">
         <v>488</v>
@@ -3413,7 +3413,7 @@
         <v>189775</v>
       </c>
       <c r="D50" t="n">
-        <v/>
+        <v>189850</v>
       </c>
       <c r="E50" t="n">
         <v>198950</v>
